--- a/dev-docs/task-260902-报价与核价建表与导入方案新规范/报价 - 数据导入与表格建表.xlsx
+++ b/dev-docs/task-260902-报价与核价建表与导入方案新规范/报价 - 数据导入与表格建表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\dev-docs\task-260902-报价与核价建表与导入方案新规范\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C64DA6-0CFE-4EA9-A7A8-6A0672BA2C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF545E40-70A6-4AF8-B2F4-430466819CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="物料" sheetId="24" r:id="rId1"/>
@@ -419,10 +419,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>外购件</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>回收值</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -464,6 +460,10 @@
   </si>
   <si>
     <t>对比项</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>客户编号</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -717,9 +717,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -771,9 +768,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -806,15 +800,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1099,25 +1097,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="38" t="s">
+      <c r="A1" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="D1" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="E1" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="E1" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="37" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1146,146 +1144,146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="H1" s="11" t="s">
+      <c r="G1" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>1</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>1</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>55</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="16.5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:14" ht="16.5">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -1309,105 +1307,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>0.08</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="9"/>
+      <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:14" ht="16.5">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>12</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="9"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="16.5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -1461,35 +1459,35 @@
       </c>
     </row>
     <row r="2" spans="1:14" s="6" customFormat="1" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
       <c r="A3" s="4"/>
@@ -1546,82 +1544,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8">
         <v>1.3959999999999999</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>1.55</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="9"/>
+      <c r="H3" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -1691,7 +1689,7 @@
       <c r="D2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>84</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -1723,7 +1721,7 @@
       <c r="D3" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>84</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -1770,92 +1768,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="5" customFormat="1" ht="16.5">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:14" ht="16.5">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -1877,7 +1875,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1900,34 +1898,34 @@
       </c>
     </row>
     <row r="2" spans="1:14" s="6" customFormat="1" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -1937,35 +1935,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="29" style="6" customWidth="1"/>
-    <col min="2" max="3" width="14.875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="9" style="6"/>
+    <col min="2" max="2" width="29" style="6" customWidth="1"/>
+    <col min="3" max="4" width="14.875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="18.625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="16.5">
+      <c r="A1" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.5">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="C2" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="21" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1991,94 +1993,94 @@
     <col min="6" max="6" width="10" style="6" customWidth="1"/>
     <col min="7" max="8" width="13.125" style="6" customWidth="1"/>
     <col min="9" max="10" width="9.125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="9.125" style="20" customWidth="1"/>
-    <col min="12" max="12" width="12.125" style="20" customWidth="1"/>
+    <col min="11" max="11" width="9.125" style="19" customWidth="1"/>
+    <col min="12" max="12" width="12.125" style="19" customWidth="1"/>
     <col min="13" max="14" width="12.875" style="6" customWidth="1"/>
     <col min="15" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="16.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="L1" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="M1" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="N1" s="32" t="s">
+      <c r="N1" s="30" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="M2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="N2" s="42" t="s">
-        <v>120</v>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="M2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="N2" s="39" t="s">
+        <v>119</v>
       </c>
       <c r="Q2" s="40"/>
       <c r="R2" s="40"/>
@@ -2086,503 +2088,503 @@
       <c r="T2" s="40"/>
     </row>
     <row r="3" spans="1:20" ht="16.5">
-      <c r="A3" s="18">
+      <c r="A3" s="17">
         <v>202601011226</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="14">
         <v>1</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>992</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="35"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9">
+      <c r="F3" s="33"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8">
         <v>1</v>
       </c>
-      <c r="I3" s="36">
+      <c r="I3" s="34">
         <f>G3+H3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="36" t="s">
+      <c r="K3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="36"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="9"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="8"/>
       <c r="Q3" s="40"/>
       <c r="R3" s="40"/>
       <c r="S3" s="40"/>
       <c r="T3" s="40"/>
     </row>
     <row r="4" spans="1:20" ht="16.5">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
       <c r="Q4" s="40"/>
       <c r="R4" s="40"/>
       <c r="S4" s="40"/>
       <c r="T4" s="40"/>
     </row>
     <row r="5" spans="1:20" ht="16.5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
       <c r="Q5" s="40"/>
       <c r="R5" s="40"/>
       <c r="S5" s="40"/>
       <c r="T5" s="40"/>
     </row>
     <row r="6" spans="1:20" ht="16.5">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
       <c r="Q6" s="40"/>
       <c r="R6" s="40"/>
       <c r="S6" s="40"/>
       <c r="T6" s="40"/>
     </row>
     <row r="7" spans="1:20" ht="16.5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
       <c r="Q7" s="40"/>
       <c r="R7" s="40"/>
       <c r="S7" s="40"/>
       <c r="T7" s="40"/>
     </row>
     <row r="8" spans="1:20" ht="16.5">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
       <c r="Q8" s="40"/>
       <c r="R8" s="40"/>
       <c r="S8" s="40"/>
       <c r="T8" s="40"/>
     </row>
     <row r="9" spans="1:20" ht="16.5">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
       <c r="Q9" s="40"/>
       <c r="R9" s="40"/>
       <c r="S9" s="40"/>
       <c r="T9" s="40"/>
     </row>
     <row r="10" spans="1:20" ht="16.5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
       <c r="Q10" s="40"/>
       <c r="R10" s="40"/>
       <c r="S10" s="40"/>
       <c r="T10" s="40"/>
     </row>
     <row r="11" spans="1:20" ht="16.5">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
       <c r="Q11" s="40"/>
       <c r="R11" s="40"/>
       <c r="S11" s="40"/>
       <c r="T11" s="40"/>
     </row>
     <row r="12" spans="1:20" ht="16.5">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
       <c r="Q12" s="40"/>
       <c r="R12" s="40"/>
       <c r="S12" s="40"/>
       <c r="T12" s="40"/>
     </row>
     <row r="13" spans="1:20" ht="16.5">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
       <c r="Q13" s="40"/>
       <c r="R13" s="40"/>
       <c r="S13" s="40"/>
       <c r="T13" s="40"/>
     </row>
     <row r="14" spans="1:20" ht="16.5">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
       <c r="Q14" s="40"/>
       <c r="R14" s="40"/>
       <c r="S14" s="40"/>
       <c r="T14" s="40"/>
     </row>
     <row r="15" spans="1:20" ht="16.5">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
       <c r="Q15" s="40"/>
       <c r="R15" s="40"/>
       <c r="S15" s="40"/>
       <c r="T15" s="40"/>
     </row>
     <row r="16" spans="1:20" ht="16.5">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
       <c r="Q16" s="40"/>
       <c r="R16" s="40"/>
       <c r="S16" s="40"/>
       <c r="T16" s="40"/>
     </row>
     <row r="17" spans="1:20" ht="16.5">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
       <c r="Q17" s="40"/>
       <c r="R17" s="40"/>
       <c r="S17" s="40"/>
       <c r="T17" s="40"/>
     </row>
     <row r="18" spans="1:20" ht="16.5">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="40"/>
       <c r="S18" s="40"/>
       <c r="T18" s="40"/>
     </row>
     <row r="19" spans="1:20" ht="16.5">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
     </row>
     <row r="20" spans="1:20" ht="16.5">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
     </row>
     <row r="21" spans="1:20" ht="16.5">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
     </row>
     <row r="22" spans="1:20" ht="16.5">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
     </row>
     <row r="23" spans="1:20" ht="16.5">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
     </row>
     <row r="24" spans="1:20" ht="16.5">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
     </row>
     <row r="25" spans="1:20" ht="16.5">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
     </row>
     <row r="26" spans="1:20" ht="16.5">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
     </row>
     <row r="27" spans="1:20" ht="16.5">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
     </row>
     <row r="28" spans="1:20" ht="16.5">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2618,532 +2620,532 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="M2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="M2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="18">
+      <c r="A3" s="17">
         <v>202601011226</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>992</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="14">
         <v>1</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14">
+      <c r="G3" s="13"/>
+      <c r="H3" s="13">
         <v>8.6842529099999997</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>8.6842529099999997</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5">
-      <c r="A4" s="18">
+      <c r="A4" s="17">
         <v>202601011226</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>992</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="14">
         <v>2</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14">
+      <c r="G4" s="13"/>
+      <c r="H4" s="13">
         <v>1.1436391800000001</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>1.1436391800000001</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5">
-      <c r="A5" s="18">
+      <c r="A5" s="17">
         <v>202601011226</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>992</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="14">
         <v>3</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16">
+      <c r="G5" s="15"/>
+      <c r="H5" s="15">
         <v>7.4418822899999997</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="15">
         <v>7.4418822899999997</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5">
-      <c r="A6" s="18">
+      <c r="A6" s="17">
         <v>202601011226</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>992</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <v>4</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16">
+      <c r="G6" s="15"/>
+      <c r="H6" s="15">
         <v>4.5622152900000001</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="15">
         <v>4.5622152900000001</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5">
-      <c r="A7" s="18">
+      <c r="A7" s="17">
         <v>202601011226</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>992</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <v>5</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16">
+      <c r="G7" s="15"/>
+      <c r="H7" s="15">
         <v>19.16624079</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>19.16624079</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:14" ht="16.5">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:14" ht="16.5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:14" ht="16.5">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:14" ht="16.5">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="1:14" ht="16.5">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="1:14" ht="16.5">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:14" ht="16.5">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" spans="1:14" ht="16.5">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
     </row>
     <row r="17" spans="1:11" ht="16.5">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
     </row>
     <row r="18" spans="1:11" ht="16.5">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
     </row>
     <row r="19" spans="1:11" ht="16.5">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
     </row>
     <row r="20" spans="1:11" ht="16.5">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
     </row>
     <row r="21" spans="1:11" ht="16.5">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
     </row>
     <row r="22" spans="1:11" ht="16.5">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
     </row>
     <row r="23" spans="1:11" ht="16.5">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
     </row>
     <row r="24" spans="1:11" ht="16.5">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
     </row>
     <row r="25" spans="1:11" ht="16.5">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
     </row>
     <row r="26" spans="1:11" ht="16.5">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:11" ht="16.5">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
     </row>
     <row r="28" spans="1:11" ht="16.5">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
     </row>
     <row r="29" spans="1:11" ht="16.5">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -3174,129 +3176,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="23" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="M2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="M2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
     </row>
     <row r="4" spans="1:14" ht="16.5">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="16.5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
     </row>
     <row r="6" spans="1:14" ht="16.5">
-      <c r="C6" s="9"/>
+      <c r="C6" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -3324,470 +3326,470 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:14" ht="16.5">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="16.5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
     </row>
     <row r="6" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:14" ht="16.5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:14" ht="16.5">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:14" ht="16.5">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:14" ht="16.5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:14" ht="16.5">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:14" ht="16.5">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:14" ht="16.5">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:14" ht="16.5">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:14" ht="16.5">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:14" ht="16.5">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" ht="16.5">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" ht="16.5">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" ht="16.5">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" ht="16.5">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" spans="1:10" ht="16.5">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" spans="1:10" ht="16.5">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" spans="1:10" ht="16.5">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="1:10" ht="16.5">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:10" ht="16.5">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
     </row>
     <row r="26" spans="1:10" ht="16.5">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
     </row>
     <row r="27" spans="1:10" ht="16.5">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
     </row>
     <row r="28" spans="1:10" ht="16.5">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
     </row>
     <row r="29" spans="1:10" ht="16.5">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
     </row>
     <row r="30" spans="1:10" ht="16.5">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
     </row>
     <row r="31" spans="1:10" ht="16.5">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
     </row>
     <row r="32" spans="1:10" ht="16.5">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
     </row>
     <row r="33" spans="1:10" ht="16.5">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
     </row>
     <row r="34" spans="1:10" ht="16.5">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="16.5">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
     </row>
     <row r="36" spans="1:10" ht="16.5">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -3797,7 +3799,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" style="6" customWidth="1"/>
@@ -3809,60 +3811,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="23" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-    </row>
-    <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -3892,184 +3885,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>1</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>992</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="14">
         <v>1</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="17">
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16">
         <v>0.138114345654515</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
     </row>
     <row r="4" spans="1:14" ht="16.5">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="16.5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:14" ht="16.5">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" spans="1:14" ht="16.5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:14" ht="16.5">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:14" ht="16.5">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:14" ht="16.5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -4094,19 +4087,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>39</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -4117,113 +4110,113 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5">
-      <c r="A2" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="A2" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="16.5">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8">
         <v>4.5</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8">
         <v>4</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8">
         <v>4</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8">
         <v>13</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>51</v>
       </c>
     </row>
